--- a/docs/downloads/经营分_鲁西省区__济滨片区_2026-10-18.xlsx
+++ b/docs/downloads/经营分_鲁西省区__济滨片区_2026-10-18.xlsx
@@ -779,17 +779,17 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>6820436771545860107</t>
+          <t>6641055395307620359</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>维也纳3好酒店（济南西站医学中心店）</t>
+          <t>7天优品酒店（济南西站大杨地铁站）</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>维也纳3好酒店(济南西客站医学中心店)</t>
+          <t>7天优品酒店(济南西站店)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -798,10 +798,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -815,7 +815,7 @@
         <v>10</v>
       </c>
       <c r="M3" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="N3" t="n">
         <v>30</v>
@@ -827,7 +827,7 @@
         <v>30</v>
       </c>
       <c r="Q3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="R3" t="n">
         <v>30</v>
@@ -867,17 +867,17 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>6641055395307620359</t>
+          <t>6820436771545860107</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>7天优品酒店（济南西站大杨地铁站）</t>
+          <t>维也纳3好酒店（济南西站医学中心店）</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>7天优品酒店(济南西站店)</t>
+          <t>维也纳3好酒店(济南西客站医学中心店)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -903,7 +903,7 @@
         <v>10</v>
       </c>
       <c r="M4" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="N4" t="n">
         <v>30</v>
@@ -915,7 +915,7 @@
         <v>30</v>
       </c>
       <c r="Q4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R4" t="n">
         <v>30</v>
@@ -1214,34 +1214,34 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>滨州市</t>
+          <t>济南市</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>7232897363956729912</t>
+          <t>7235888053255702528</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>7天酒店（滨州惠民南关大街店）</t>
+          <t>希岸酒店（济南火车站大观园省立医院店）</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>7天酒店(滨州惠民南关大街店)</t>
+          <t>希岸酒店(济南火车站大观园省立医院店)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H8" t="n">
         <v>95</v>
       </c>
       <c r="I8" t="n">
-        <v>-5</v>
+        <v>5</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -1302,22 +1302,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>济南市</t>
+          <t>滨州市</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>7235888053255702528</t>
+          <t>7325344371035867190</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>希岸酒店（济南火车站大观园省立医院店）</t>
+          <t>潮漫酒店（邹平黄山时代广场店）</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>希岸酒店(济南火车站大观园省立医院店)</t>
+          <t>潮漫酒店(邹平新邹时代广场店)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1329,11 +1329,11 @@
         <v>95</v>
       </c>
       <c r="I9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>提质量,拿收益</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -1343,7 +1343,7 @@
         <v>10</v>
       </c>
       <c r="M9" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="N9" t="n">
         <v>30</v>
@@ -1355,7 +1355,7 @@
         <v>30</v>
       </c>
       <c r="Q9" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R9" t="n">
         <v>30</v>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>滨州市</t>
+          <t>济南市</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>7325344371035867190</t>
+          <t>7278635803725531155</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>潮漫酒店（邹平黄山时代广场店）</t>
+          <t>白玉兰商务酒店（山东国际会展中心二环西路店）</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>潮漫酒店(邹平新邹时代广场店)</t>
+          <t>白玉兰酒店(山东国际会展中心店)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>提质量,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1431,13 +1431,13 @@
         <v>10</v>
       </c>
       <c r="M10" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N10" t="n">
         <v>30</v>
       </c>
       <c r="O10" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="P10" t="n">
         <v>30</v>
@@ -1483,22 +1483,22 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>7278635803725531155</t>
+          <t>7235879444299941943</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>白玉兰商务酒店（山东国际会展中心二环西路店）</t>
+          <t>麗枫酒店（济南宜家家居山东国际会展中心店）</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>白玉兰酒店(山东国际会展中心店)</t>
+          <t>麗枫酒店(济南宜家家居山东国际会展中心店)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>提质量,拿收益</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1519,13 +1519,13 @@
         <v>10</v>
       </c>
       <c r="M11" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="N11" t="n">
         <v>30</v>
       </c>
       <c r="O11" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="P11" t="n">
         <v>30</v>
@@ -1566,22 +1566,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>济南市</t>
+          <t>滨州市</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>7235879444299941943</t>
+          <t>7232897363956729912</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>麗枫酒店（济南宜家家居山东国际会展中心店）</t>
+          <t>7天酒店（滨州惠民南关大街店）</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>麗枫酒店(济南宜家家居山东国际会展中心店)</t>
+          <t>7天酒店(滨州惠民南关大街店)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1590,14 +1590,14 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="I12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>提质量,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -1607,7 +1607,7 @@
         <v>10</v>
       </c>
       <c r="M12" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N12" t="n">
         <v>30</v>
@@ -1619,7 +1619,7 @@
         <v>30</v>
       </c>
       <c r="Q12" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="R12" t="n">
         <v>30</v>
@@ -1674,7 +1674,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -2275,22 +2275,22 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>7284844940104828986</t>
+          <t>7565978757203232811</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>喆啡酒店（山东国际会展中心济南西站宜家店）</t>
+          <t>锦江之星5.0（济南西站印象济南店）</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>喆·啡酒店(山东国际会展中心济南西站宜家店)</t>
+          <t>锦江之星5.0酒店(济南西站印象济南店)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H20" t="n">
@@ -2301,7 +2301,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>拿收益</t>
+          <t>提质量,拿收益</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -2317,13 +2317,13 @@
         <v>30</v>
       </c>
       <c r="O20" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="P20" t="n">
         <v>30</v>
       </c>
       <c r="Q20" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="R20" t="n">
         <v>30</v>
@@ -2358,22 +2358,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>济南市</t>
+          <t>滨州市</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>6965388806476269583</t>
+          <t>7226645831813466152</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>希岸酒店（济南西站店）</t>
+          <t>凯里亚德酒店（邹平黛溪湖公园店）</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>希岸酒店(济南西站店)</t>
+          <t>凯里亚德酒店(邹平黛溪湖公园店)</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -2382,14 +2382,14 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>提质量,拿收益</t>
+          <t>稳房源,拿收益</t>
         </is>
       </c>
       <c r="K21" t="n">
@@ -2399,19 +2399,19 @@
         <v>10</v>
       </c>
       <c r="M21" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="N21" t="n">
         <v>30</v>
       </c>
       <c r="O21" t="n">
+        <v>30</v>
+      </c>
+      <c r="P21" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q21" t="n">
         <v>25</v>
-      </c>
-      <c r="P21" t="n">
-        <v>30</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>20</v>
       </c>
       <c r="R21" t="n">
         <v>30</v>
@@ -2446,22 +2446,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>济南市</t>
+          <t>滨州市</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>7565978757203232811</t>
+          <t>7122302162603886628</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>锦江之星5.0（济南西站印象济南店）</t>
+          <t>7天优品Premium（滨州胡集店）</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>锦江之星5.0酒店(济南西站印象济南店)</t>
+          <t>7天优品酒店(滨州胡集店)</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2470,7 +2470,7 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
@@ -2493,7 +2493,7 @@
         <v>30</v>
       </c>
       <c r="O22" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="P22" t="n">
         <v>30</v>
@@ -2534,22 +2534,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>滨州市</t>
+          <t>济南市</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>7226645831813466152</t>
+          <t>7235875063717693477</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>凯里亚德酒店（邹平黛溪湖公园店）</t>
+          <t>丽怡酒店（山东国际会展中心八里桥地铁站店）</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>凯里亚德酒店(邹平黛溪湖公园店)</t>
+          <t>丽怡酒店(山东国际会展中心八里桥地铁站店)</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2558,14 +2558,14 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>稳房源,拿收益</t>
+          <t>拿收益</t>
         </is>
       </c>
       <c r="K23" t="n">
@@ -2575,7 +2575,7 @@
         <v>10</v>
       </c>
       <c r="M23" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="N23" t="n">
         <v>30</v>
@@ -2587,7 +2587,7 @@
         <v>30</v>
       </c>
       <c r="Q23" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="R23" t="n">
         <v>30</v>
@@ -2622,38 +2622,38 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>滨州市</t>
+          <t>济南市</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>7122302162603886628</t>
+          <t>7284844940104828986</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>7天优品Premium（滨州胡集店）</t>
+          <t>喆啡酒店（山东国际会展中心济南西站宜家店）</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>7天优品酒店(滨州胡集店)</t>
+          <t>喆·啡酒店(山东国际会展中心济南西站宜家店)</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H24" t="n">
         <v>110</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>提质量,拿收益</t>
+          <t>拿收益</t>
         </is>
       </c>
       <c r="K24" t="n">
@@ -2669,13 +2669,13 @@
         <v>30</v>
       </c>
       <c r="O24" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="P24" t="n">
         <v>30</v>
       </c>
       <c r="Q24" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="R24" t="n">
         <v>30</v>
@@ -2715,17 +2715,17 @@
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>7235875063717693477</t>
+          <t>6965388806476269583</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>丽怡酒店（山东国际会展中心八里桥地铁站店）</t>
+          <t>希岸酒店（济南西站店）</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>丽怡酒店(山东国际会展中心八里桥地铁站店)</t>
+          <t>希岸酒店(济南西站店)</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2737,7 +2737,7 @@
         <v>110</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
